--- a/example-spreadsheets/study-tasks/task-02/task02_grading.xlsx
+++ b/example-spreadsheets/study-tasks/task-02/task02_grading.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t xml:space="preserve">Task 2</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t xml:space="preserve">What happens if Alices score changes to 96 and why ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change the grading scale so that Alice receives grade 6</t>
   </si>
 </sst>
 </file>
@@ -310,7 +313,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -507,6 +510,14 @@
       </c>
       <c r="B28" s="3" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
